--- a/Failed_Test_Cases.xlsx
+++ b/Failed_Test_Cases.xlsx
@@ -2500,7 +2500,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1828ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1926ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1713ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1728ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1553ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1590ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1804ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1871ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1703ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1793ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1884ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1885ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1615ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1655ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1687ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1587ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1885ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1661ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1736ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1931ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1701ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1734ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1761ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1572ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1783ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1920ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1895ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1930ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1821ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1607ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1833ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1732ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1725ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1558ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>

--- a/Failed_Test_Cases.xlsx
+++ b/Failed_Test_Cases.xlsx
@@ -2500,7 +2500,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1926ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1781ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1728ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1879ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1590ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1871ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1871ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1793ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1793ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1623ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1885ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1841ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1655ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1930ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1587ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1738ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1661ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1609ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1931ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1585ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1734ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1874ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1572ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1743ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1920ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1640ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1930ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1706ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1607ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1558ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1732ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1580ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1558ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1714ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
